--- a/data/trans_dic/P34B03_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P34B03_R-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación, 3 veces por semana o más</t>
+          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic, correr, natación, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,74</t>
+          <t>3,9; 6,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,52</t>
+          <t>6,53; 10,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,86</t>
+          <t>3,32; 6,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,32</t>
+          <t>2,3; 4,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,47</t>
+          <t>2,2; 4,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,27</t>
+          <t>1,51; 3,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,92</t>
+          <t>3,34; 4,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,59</t>
+          <t>4,29; 6,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,27</t>
+          <t>2,51; 4,18</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,91; 19,43</t>
+          <t>15,97; 19,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,8; 19,09</t>
+          <t>15,64; 19,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 20,51</t>
+          <t>11,71; 20,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,3</t>
+          <t>5,87; 8,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 11,86</t>
+          <t>9,1; 11,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 8,5</t>
+          <t>5,39; 8,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,51; 13,74</t>
+          <t>11,48; 13,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,97; 15,11</t>
+          <t>12,95; 15,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 14,15</t>
+          <t>9,98; 14,16</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,56; 32,09</t>
+          <t>23,32; 32,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,58; 30,1</t>
+          <t>22,39; 30,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,75; 26,11</t>
+          <t>18,9; 25,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,03; 18,05</t>
+          <t>11,2; 17,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,19; 20,82</t>
+          <t>14,28; 20,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,58; 19,95</t>
+          <t>14,66; 19,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,38; 24,22</t>
+          <t>18,19; 23,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,3; 24,47</t>
+          <t>19,43; 24,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 22,09</t>
+          <t>17,63; 21,98</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,09; 16,82</t>
+          <t>14,32; 16,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,62; 18,22</t>
+          <t>15,64; 18,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,92; 18,64</t>
+          <t>12,82; 18,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,46</t>
+          <t>5,73; 7,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,52; 10,59</t>
+          <t>8,55; 10,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,05</t>
+          <t>6,45; 8,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,2; 11,79</t>
+          <t>10,21; 11,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,24; 13,89</t>
+          <t>12,31; 13,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 13,27</t>
+          <t>10,26; 13,18</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación, 3 veces por semana o más</t>
+          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic, correr, natación, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>38010; 65566</t>
+          <t>37953; 66325</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48028; 79387</t>
+          <t>49282; 79468</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16749; 35308</t>
+          <t>17107; 35561</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30522; 57847</t>
+          <t>30730; 58203</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20978; 44495</t>
+          <t>21853; 45015</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11541; 24576</t>
+          <t>11361; 25530</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75952; 113744</t>
+          <t>77232; 114892</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75645; 115257</t>
+          <t>75025; 115436</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32347; 54140</t>
+          <t>31827; 52945</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>312407; 381523</t>
+          <t>313696; 382333</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>327988; 396335</t>
+          <t>324781; 396338</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>279390; 469381</t>
+          <t>267997; 470353</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>104132; 145790</t>
+          <t>102998; 144192</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>177173; 235830</t>
+          <t>180889; 238176</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>116795; 190025</t>
+          <t>120573; 191338</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>428329; 511149</t>
+          <t>427163; 512874</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>527076; 614107</t>
+          <t>526206; 614530</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>451559; 640084</t>
+          <t>451286; 640627</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>113390; 154390</t>
+          <t>112206; 155102</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>123484; 164612</t>
+          <t>122443; 165309</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>121261; 168836</t>
+          <t>122235; 166831</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50575; 82781</t>
+          <t>51366; 81564</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>77949; 114328</t>
+          <t>78426; 113362</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96283; 131795</t>
+          <t>96839; 132041</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>172748; 227619</t>
+          <t>170960; 224951</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>211518; 268195</t>
+          <t>212923; 268104</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>229124; 288697</t>
+          <t>230377; 287288</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>481434; 574772</t>
+          <t>489434; 578814</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>527578; 615419</t>
+          <t>528218; 614652</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>445756; 643128</t>
+          <t>442263; 638575</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>200768; 265159</t>
+          <t>203516; 266207</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>300775; 374109</t>
+          <t>302118; 370131</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>235911; 330045</t>
+          <t>235438; 326497</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>711129; 821515</t>
+          <t>711634; 815385</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>845651; 960007</t>
+          <t>850466; 966243</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744338; 941814</t>
+          <t>728614; 935544</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B03_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P34B03_R-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,82</t>
+          <t>3,9; 6,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,53</t>
+          <t>6,5; 10,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,91</t>
+          <t>3,37; 6,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,35</t>
+          <t>2,3; 4,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,53</t>
+          <t>2,15; 4,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,39</t>
+          <t>1,53; 3,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 4,97</t>
+          <t>3,28; 5,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,6</t>
+          <t>4,44; 6,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,18</t>
+          <t>2,57; 4,25</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,97; 19,47</t>
+          <t>15,98; 19,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,64; 19,09</t>
+          <t>15,76; 19,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 20,55</t>
+          <t>17,17; 21,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 8,21</t>
+          <t>5,99; 8,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,1; 11,98</t>
+          <t>9,07; 11,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,56</t>
+          <t>7,14; 9,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,48; 13,79</t>
+          <t>11,57; 13,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,95; 15,12</t>
+          <t>12,95; 15,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 14,16</t>
+          <t>12,68; 15,16</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,32; 32,23</t>
+          <t>23,46; 32,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,39; 30,23</t>
+          <t>22,34; 30,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,9; 25,8</t>
+          <t>18,87; 26,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,2; 17,78</t>
+          <t>11,11; 18,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,28; 20,64</t>
+          <t>14,3; 20,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 19,99</t>
+          <t>14,3; 19,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 23,94</t>
+          <t>18,27; 23,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,43; 24,46</t>
+          <t>19,48; 24,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,63; 21,98</t>
+          <t>17,52; 21,78</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,32; 16,94</t>
+          <t>14,38; 16,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,64; 18,2</t>
+          <t>15,61; 18,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 18,51</t>
+          <t>16,04; 19,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 7,49</t>
+          <t>5,76; 7,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,55; 10,48</t>
+          <t>8,54; 10,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 8,95</t>
+          <t>7,74; 9,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 11,7</t>
+          <t>10,17; 11,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,31; 13,98</t>
+          <t>12,29; 13,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 13,18</t>
+          <t>12,04; 13,8</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24758</t>
+          <t>29160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17055</t>
+          <t>18316</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41812</t>
+          <t>47475</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37953; 66325</t>
+          <t>37913; 67625</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49282; 79468</t>
+          <t>49054; 78494</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17107; 35561</t>
+          <t>19479; 39711</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30730; 58203</t>
+          <t>30825; 58595</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21853; 45015</t>
+          <t>21401; 45373</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11361; 25530</t>
+          <t>12556; 26593</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77232; 114892</t>
+          <t>75766; 117862</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75025; 115436</t>
+          <t>77576; 116969</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31827; 52945</t>
+          <t>35938; 59473</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401658</t>
+          <t>429744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>157908</t>
+          <t>180245</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>559567</t>
+          <t>609990</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>313696; 382333</t>
+          <t>313930; 384770</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>324781; 396338</t>
+          <t>327316; 396561</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>267997; 470353</t>
+          <t>382660; 475435</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>102998; 144192</t>
+          <t>105103; 147287</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>180889; 238176</t>
+          <t>180241; 237486</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>120573; 191338</t>
+          <t>154843; 205756</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>427163; 512874</t>
+          <t>430430; 511988</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>526206; 614530</t>
+          <t>526178; 613530</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>451286; 640627</t>
+          <t>557708; 666504</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143631</t>
+          <t>157760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>114220</t>
+          <t>123821</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>257851</t>
+          <t>281581</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>112206; 155102</t>
+          <t>112903; 156449</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122443; 165309</t>
+          <t>122150; 164196</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122235; 166831</t>
+          <t>134271; 185053</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51366; 81564</t>
+          <t>50944; 84234</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78426; 113362</t>
+          <t>78512; 114367</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96839; 132041</t>
+          <t>105064; 144144</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>170960; 224951</t>
+          <t>171684; 224613</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>212923; 268104</t>
+          <t>213477; 269800</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>230377; 287288</t>
+          <t>253473; 315099</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>570047</t>
+          <t>616664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>289183</t>
+          <t>322382</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>859230</t>
+          <t>939047</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>489434; 578814</t>
+          <t>491579; 577694</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>528218; 614652</t>
+          <t>527127; 612051</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>442263; 638575</t>
+          <t>564314; 673460</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>203516; 266207</t>
+          <t>204791; 266047</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>302118; 370131</t>
+          <t>301744; 375112</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>235438; 326497</t>
+          <t>288390; 357180</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>711634; 815385</t>
+          <t>708882; 814861</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>850466; 966243</t>
+          <t>849431; 962850</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>728614; 935544</t>
+          <t>871901; 999863</t>
         </is>
       </c>
     </row>
